--- a/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,35</t>
+          <t>0,0; 16,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 14,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 12,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 8,87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,74</t>
+          <t>1,74; 14,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,02</t>
+          <t>0,52; 5,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,85</t>
+          <t>1,75; 8,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,2</t>
+          <t>0,6; 5,01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,12</t>
+          <t>1,21; 10,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,54</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,11</t>
+          <t>0,53; 5,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,64</t>
+          <t>0,57; 5,03</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,4</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,31</t>
+          <t>2,6; 20,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,35</t>
+          <t>0,0; 21,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,39</t>
+          <t>0,0; 16,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 33,89</t>
+          <t>4,93; 35,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,57</t>
+          <t>2,62; 14,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,11</t>
+          <t>2,69; 22,18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 9,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,83</t>
+          <t>0,5; 5,12</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,58</t>
+          <t>0,78; 6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,65</t>
+          <t>0,77; 6,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,55</t>
+          <t>0,41; 3,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,49</t>
+          <t>0,43; 4,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,8</t>
+          <t>0,83; 4,82</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,36; 2,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,47</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,15</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,19</t>
+          <t>0,36; 2,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,78; 3,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,8; 3,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,74</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,37; 3,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,37; 3,15</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4075</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3802</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2559</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3066</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3945</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5184</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3209</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>923; 7522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4212</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5633</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3974</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>631; 6373</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1937; 9749</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>657; 5526</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3435</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3281</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4155</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2312</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>564; 4965</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4365</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4260</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>443; 4882</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>556; 4905</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3654</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2837</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>677; 5317</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3303</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4493</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>841; 6017</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3021</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1404; 7955</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>864; 7123</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3355</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3687</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3022</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4051</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3454</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5828</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3895</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3849</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3502</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>653; 6623</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>606; 5350</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>613; 5173</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4565</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4567</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>639; 5511</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>631; 6448</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1308; 7611</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9286</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>15504</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7840</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5024; 15210</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4915; 15038</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1317; 7925</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11182</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2928; 11394</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3691; 12639</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>9897; 23270</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>10024; 23039</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 18,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,27</t>
+          <t>0,0; 14,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 13,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,87</t>
+          <t>0,0; 8,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 14,18</t>
+          <t>1,79; 14,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,87</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,67</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,22</t>
+          <t>0,52; 5,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,81</t>
+          <t>1,47; 8,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,01</t>
+          <t>0,6; 5,07</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 12,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,67</t>
+          <t>1,21; 10,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,88</t>
+          <t>0,53; 5,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,03</t>
+          <t>0,57; 5,6</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 20,4</t>
+          <t>2,6; 22,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,95</t>
+          <t>0,0; 18,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,26</t>
+          <t>0,0; 16,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 35,26</t>
+          <t>4,95; 37,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,81</t>
+          <t>2,66; 14,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 22,18</t>
+          <t>2,64; 23,81</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 13,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,22 +1363,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,12</t>
+          <t>0,51; 5,55</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,87</t>
+          <t>0,78; 7,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,53</t>
+          <t>0,78; 6,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,54</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,36</t>
+          <t>0,52; 4,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,82</t>
+          <t>0,81; 4,87</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,23</t>
+          <t>0,35; 2,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,3</t>
+          <t>1,49; 4,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,15</t>
+          <t>1,45; 4,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,19</t>
+          <t>0,36; 2,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,06</t>
+          <t>0,78; 3,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,1</t>
+          <t>0,78; 3,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,23</t>
+          <t>1,35; 3,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,15</t>
+          <t>1,24; 3,15</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3170</t>
+          <t>0; 3490</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4075</t>
+          <t>0; 4261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3802</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2559</t>
+          <t>0; 2576</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5184</t>
+          <t>0; 5252</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3209</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923; 7522</t>
+          <t>952; 7644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4212</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5633</t>
+          <t>0; 5115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3974</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 4397</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>631; 6373</t>
+          <t>635; 6147</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1937; 9749</t>
+          <t>1625; 9516</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>657; 5526</t>
+          <t>658; 5589</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3435</t>
+          <t>0; 2646</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>0; 3763</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>0; 5144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2312</t>
+          <t>0; 2753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>564; 4965</t>
+          <t>563; 4821</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4365</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 5075</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>443; 4882</t>
+          <t>439; 4938</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>556; 4905</t>
+          <t>557; 5459</t>
         </is>
       </c>
     </row>
@@ -2513,17 +2513,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2837</t>
+          <t>0; 3012</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>677; 5317</t>
+          <t>678; 5780</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3303</t>
+          <t>0; 2834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,27 +2533,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4530</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>841; 6017</t>
+          <t>846; 6341</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3118</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1404; 7955</t>
+          <t>1428; 7597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>864; 7123</t>
+          <t>849; 7645</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3355</t>
+          <t>0; 4828</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 3018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3022</t>
+          <t>0; 3379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4051</t>
+          <t>0; 3678</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3454</t>
+          <t>0; 3293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5828</t>
+          <t>0; 6541</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3895</t>
+          <t>0; 3851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2864,22 +2864,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3502</t>
+          <t>0; 3273</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 3207</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>653; 6623</t>
+          <t>655; 7183</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>606; 5350</t>
+          <t>609; 6052</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>613; 5173</t>
+          <t>617; 5348</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4565</t>
+          <t>0; 4256</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3378</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4567</t>
+          <t>0; 5155</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>639; 5511</t>
+          <t>0; 5378</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>631; 6448</t>
+          <t>765; 6359</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1308; 7611</t>
+          <t>1275; 7683</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1266; 7840</t>
+          <t>1237; 7453</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5024; 15210</t>
+          <t>5259; 15848</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4915; 15038</t>
+          <t>5262; 16245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1317; 7925</t>
+          <t>1299; 8508</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2840; 11182</t>
+          <t>2848; 11619</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2928; 11394</t>
+          <t>2859; 11704</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3691; 12639</t>
+          <t>3505; 12640</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9897; 23270</t>
+          <t>9716; 22836</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10024; 23039</t>
+          <t>9037; 23031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,92</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 14,41</t>
+          <t>0,0; 8,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>1,78; 14,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,03</t>
+          <t>0,52; 5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,6</t>
+          <t>1,46; 7,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,07</t>
+          <t>0,59; 5,2</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 10,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,2; 11,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,95</t>
+          <t>0,52; 6,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,6</t>
+          <t>0,57; 5,64</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,17</t>
+          <t>0,0; 18,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,84</t>
+          <t>4,98; 33,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>2,6; 22,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 37,15</t>
+          <t>0,0; 18,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 14,15</t>
+          <t>2,68; 15,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 23,81</t>
+          <t>2,64; 22,11</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,55</t>
+          <t>0,51; 5,83</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,77</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,75</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,78; 6,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,77; 6,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,41; 3,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,3</t>
+          <t>0,43; 4,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,87</t>
+          <t>0,83; 4,8</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,12</t>
+          <t>0,37; 2,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,48</t>
+          <t>0,77; 3,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>0,66; 3,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,35</t>
+          <t>0,36; 2,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>1,51; 4,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,18</t>
+          <t>1,4; 4,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,77</t>
+          <t>0,48; 1,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,17</t>
+          <t>1,42; 3,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,15</t>
+          <t>1,35; 3,12</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,14 +1755,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>826</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3490</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4261</t>
+          <t>0; 3747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2576</t>
+          <t>0; 3558</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>0; 3413</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3705</t>
+          <t>0; 3199</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 4553</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1353</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 6037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>952; 7644</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4172</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5115</t>
+          <t>0; 3646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>943; 7818</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4397</t>
+          <t>0; 4202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>635; 6147</t>
+          <t>634; 6131</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1625; 9516</t>
+          <t>1614; 8684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>658; 5589</t>
+          <t>649; 5732</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3360</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3763</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1826</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5144</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2753</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>563; 4821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 2255</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>560; 5174</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5075</t>
+          <t>0; 4351</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>439; 4938</t>
+          <t>431; 5071</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>557; 5459</t>
+          <t>557; 5503</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2195</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>662</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>678; 5780</t>
+          <t>0; 5081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2834</t>
+          <t>850; 5785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>679; 5815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>846; 6341</t>
+          <t>0; 2760</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3118</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1428; 7597</t>
+          <t>1437; 8362</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>849; 7645</t>
+          <t>847; 7100</t>
         </is>
       </c>
     </row>
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>735</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>729</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4828</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3419</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3548</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>0; 3463</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3678</t>
+          <t>0; 3668</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1750</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3549</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6541</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 6591</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>0; 3075</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3207</t>
+          <t>0; 3289</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>655; 7183</t>
+          <t>657; 7542</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1958</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3447</t>
+          <t>0; 4844</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>609; 6052</t>
+          <t>0; 3490</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>617; 5348</t>
+          <t>0; 5073</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>0; 3783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2843</t>
+          <t>611; 5122</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5155</t>
+          <t>607; 5272</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5378</t>
+          <t>638; 5527</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>765; 6359</t>
+          <t>632; 6639</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1275; 7683</t>
+          <t>1317; 7583</t>
         </is>
       </c>
     </row>
@@ -3064,27 +3064,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>9104</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1237; 7453</t>
+          <t>1331; 7935</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5259; 15848</t>
+          <t>2800; 11351</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5262; 16245</t>
+          <t>2440; 11413</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1299; 8508</t>
+          <t>1255; 7349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2848; 11619</t>
+          <t>5329; 15840</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2859; 11704</t>
+          <t>5089; 15050</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3505; 12640</t>
+          <t>3427; 12413</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9716; 22836</t>
+          <t>10200; 22903</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9037; 23031</t>
+          <t>9859; 22801</t>
         </is>
       </c>
     </row>
